--- a/样品寄送模版.xlsx
+++ b/样品寄送模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14060" activeTab="1"/>
+    <workbookView windowWidth="29400" windowHeight="14060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>外部平台单号</t>
   </si>
@@ -381,18 +381,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>A2</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
@@ -401,7 +394,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -410,7 +402,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
@@ -419,7 +410,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -433,7 +423,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -442,7 +431,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
@@ -451,7 +439,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -460,7 +447,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
@@ -469,6 +455,15 @@
   </si>
   <si>
     <t>哇！仙楂干噎（干噎酸奶）</t>
+  </si>
+  <si>
+    <t>婴幼儿奶奶面</t>
+  </si>
+  <si>
+    <t>益生菌酸奶如意溶豆（原味）</t>
+  </si>
+  <si>
+    <t>益生菌酸奶如意溶豆（草莓味）</t>
   </si>
 </sst>
 </file>
@@ -481,7 +476,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -547,20 +542,23 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1051,152 +1049,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1260,10 +1258,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1278,10 +1282,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1340,6 +1344,12 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00000000"/>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1651,77 +1661,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:16">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="21" customFormat="1" ht="24.95" customHeight="1" spans="1:16">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25">
+    <row r="2" s="23" customFormat="1" ht="24.95" customHeight="1" spans="1:16">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="27" t="s">
+        <v>46184</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
       <c r="N2" s="7"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="29"/>
+      <c r="P2" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2343,16 +2353,28 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="22">
+        <v>6978836201134</v>
+      </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="22">
+        <v>6978836201165</v>
+      </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
+      <c r="A78" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" s="22">
+        <v>6978836201172</v>
+      </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="4"/>

--- a/样品寄送模版.xlsx
+++ b/样品寄送模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14060" activeTab="1"/>
+    <workbookView windowWidth="28260" windowHeight="14060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>外部平台单号</t>
   </si>
@@ -381,6 +381,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>A2</t>
     </r>
     <r>
@@ -418,6 +423,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>希腊</t>
     </r>
     <r>
@@ -464,6 +474,9 @@
   </si>
   <si>
     <t>益生菌酸奶如意溶豆（草莓味）</t>
+  </si>
+  <si>
+    <t>仙楂干噎500g</t>
   </si>
 </sst>
 </file>
@@ -1714,7 +1727,7 @@
       <c r="A2" s="26"/>
       <c r="B2" s="27">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46203</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -2377,8 +2390,12 @@
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
+      <c r="A79" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="22">
+        <v>6978836201103</v>
+      </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="4"/>
